--- a/LubanConfig/MiniTemplate/Datas/基础数据/#消除倍率表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#消除倍率表.xlsx
@@ -246,6 +246,36 @@
     <t>可操作列1</t>
   </si>
   <si>
+    <t>方块层数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块层数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块层数3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块上的小兵数1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块上的小兵数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块上的小兵数3</t>
+  </si>
+  <si>
+    <t>方块上的小兵数4</t>
+  </si>
+  <si>
+    <t>可操作列9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>方块下落速度0.7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -318,36 +348,6 @@
   </si>
   <si>
     <t>方块下落速度0.30</t>
-  </si>
-  <si>
-    <t>方块层数1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块层数2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块层数3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块上的小兵数1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块上的小兵数2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块上的小兵数3</t>
-  </si>
-  <si>
-    <t>方块上的小兵数4</t>
-  </si>
-  <si>
-    <t>可操作列9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="33" spans="2:4" ht="15.75" x14ac:dyDescent="0.2">
       <c r="C33" s="6" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D33" s="7">
         <v>0.95</v>
@@ -1245,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D42" s="16">
         <v>1.0989010989010988</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C43" s="15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D43" s="16">
         <v>1.0869565217391304</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C44" s="15" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D44" s="16">
         <v>1.0526315789473684</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C45" s="15" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D45" s="16">
         <v>1</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C46" s="15" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D46" s="16">
         <v>0.9380863039399624</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C47" s="15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D47" s="16">
         <v>0.88339222614840984</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C48" s="15" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D48" s="16">
         <v>0.8347245409015025</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D49" s="16">
         <v>0.79113924050632911</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D50" s="16">
         <v>0.75187969924812026</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D51" s="16">
         <v>0.71633237822349571</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D52" s="16">
         <v>0.6839945280437757</v>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="15" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D53" s="16">
         <v>0.65445026178010468</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="15" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D54" s="16">
         <v>0.62735257214554574</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="15" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D55" s="16">
         <v>0.60240963855421681</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C56" s="15" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D56" s="16">
         <v>0.50150451354062187</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C57" s="15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D57" s="16">
         <v>0.42955326460481097</v>
@@ -1373,7 +1373,7 @@
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C58" s="15" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D58" s="16">
         <v>0.37565740045078888</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C59" s="15" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D59" s="16">
         <v>0.33377837116154868</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C60" s="15" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D60" s="16">
         <v>0.3003003003003003</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C61" s="15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D61" s="16">
         <v>0.27292576419213971</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C62" s="15" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D62" s="16">
         <v>0.2501250625312656</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C63" s="15" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D63" s="16">
         <v>0.23084025854108953</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C64" s="15" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D64" s="16">
         <v>0.2143163309044149</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C65" s="15" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D65" s="16">
         <v>0.2</v>
@@ -1475,7 +1475,7 @@
         <v>23</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D70" s="17">
         <v>1</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C71" s="12" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D71" s="17">
         <v>0.96</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C72" s="12" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D72" s="17">
         <v>0.89999999999999991</v>
@@ -1521,7 +1521,7 @@
         <v>27</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D75" s="19">
         <v>0</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C76" s="12" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D76" s="19">
         <v>0.14300000000000002</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C77" s="12" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D77" s="19">
         <v>0.28499999999999992</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C78" s="12" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D78" s="19">
         <v>0.42900000000000005</v>
